--- a/G3 - L1 + L2/kahoot_G3_L1L2_24.xlsx
+++ b/G3 - L1 + L2/kahoot_G3_L1L2_24.xlsx
@@ -238,22 +238,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">溫蒂幾歲？</t>
+          <t xml:space="preserve">Wendy 幾歲？</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的名字是溫蒂。</t>
+          <t xml:space="preserve">你的名字是 Wendy。</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">我是溫蒂的。</t>
+          <t xml:space="preserve">我是 Wendy 的。</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">我的名字是溫蒂。</t>
+          <t xml:space="preserve">我的名字是 Wendy。</t>
         </is>
       </c>
       <c r="G13">
@@ -268,7 +268,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">「我是艾倫。」英文怎麼說？</t>
+          <t xml:space="preserve">「我是 Alan。」英文怎麼說？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">

--- a/G3 - L1 + L2/kahoot_G3_L1L2_24.xlsx
+++ b/G3 - L1 + L2/kahoot_G3_L1L2_24.xlsx
@@ -238,7 +238,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wendy 幾歲？</t>
+          <t xml:space="preserve">我的名字是什麼？</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -273,17 +273,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t xml:space="preserve">I am is Alan.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I'm Alan.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t xml:space="preserve">My Alan.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I'm Alan.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I Alan.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -413,22 +413,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t xml:space="preserve">How</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How old</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How are</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">What</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How old</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Who</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How</t>
         </is>
       </c>
       <c r="G18">
@@ -728,22 +728,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t xml:space="preserve">I’m nine year old.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I’m nine years old.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t xml:space="preserve">I’m Mike.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I’m nine years old.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How old are you?</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">My name is nine.</t>
+          <t xml:space="preserve">You’re nine years old.</t>
         </is>
       </c>
       <c r="G27">
@@ -903,17 +903,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">I’m eight years old.</t>
+          <t xml:space="preserve">I’m eight.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">I’m eight.</t>
+          <t xml:space="preserve">Your name is Ken.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your name is Ken.</t>
+          <t xml:space="preserve">My name are Ken.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
